--- a/src/src/main/webapp/portal/zkb/course/APM_ZKB_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/course/APM_ZKB_Course_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07A8D59A-64C5-4AEC-BD8C-534CEDABA13E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB90ADF5-49AF-4B6E-B236-C41B2FF67F7D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1095" windowWidth="21570" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="智康保课程" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>课程名称</t>
+  </si>
+  <si>
+    <t>课程描述</t>
   </si>
 </sst>
 </file>
@@ -351,6 +354,7 @@
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
     <col min="5" max="5" width="30.42578125" customWidth="1"/>
     <col min="6" max="6" width="28.85546875" customWidth="1"/>
   </cols>
@@ -363,7 +367,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>

--- a/src/src/main/webapp/portal/zkb/course/APM_ZKB_Course_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/course/APM_ZKB_Course_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB90ADF5-49AF-4B6E-B236-C41B2FF67F7D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E99C6E8-200F-4E37-BCF8-753EA28BAA28}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1095" windowWidth="21570" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="智康保课程" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>课程描述</t>
+  </si>
+  <si>
+    <t>modality</t>
   </si>
 </sst>
 </file>
@@ -349,17 +352,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" customWidth="1"/>
+    <col min="7" max="7" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -367,15 +370,18 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
